--- a/output/pdf_financials_xlsx/YMC.xlsx
+++ b/output/pdf_financials_xlsx/YMC.xlsx
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.027526</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.046302</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.483165</v>
       </c>
     </row>
     <row r="93">
@@ -3173,7 +3173,11 @@
           <t>Reserves 6 5,299,253</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3699,7 +3703,11 @@
           <t>Reserves 6 3,483,165</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -4184,7 +4192,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>0.027526</v>
       </c>

--- a/output/pdf_financials_xlsx/YMC.xlsx
+++ b/output/pdf_financials_xlsx/YMC.xlsx
@@ -618,10 +618,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.13437</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.155725</v>
       </c>
     </row>
     <row r="13">
@@ -884,7 +884,7 @@
         <v>-0.240475</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.98701</v>
+        <v>-2.12138</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>-0.240475</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.98661</v>
+        <v>-2.12098</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">

--- a/output/pdf_financials_xlsx/YMC.xlsx
+++ b/output/pdf_financials_xlsx/YMC.xlsx
@@ -536,10 +536,10 @@
         <v>0.039105</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.050191</v>
+        <v>0.177037</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.154517</v>
+        <v>0.288044</v>
       </c>
     </row>
     <row r="8">
@@ -584,10 +584,10 @@
         <v>0.131982</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.33585</v>
+        <v>0.462696</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.5155960000000001</v>
+        <v>0.649123</v>
       </c>
     </row>
     <row r="11">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.0009829999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009365999999999999</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2628,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009365999999999999</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
         <v>-0.251091</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.781865</v>
+        <v>-1.791231</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -4498,7 +4498,11 @@
           <t>Accretion 4,679</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -4864,7 +4868,11 @@
           <t>Private placement 11,225,000</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -5387,7 +5395,11 @@
           <t>Accretion 983</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -6462,7 +6474,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -6954,7 +6970,11 @@
           <t>Management and director fees 10 553,541</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -7541,7 +7561,11 @@
           <t>Management and director fees 10 133,527</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -8065,7 +8089,11 @@
           <t>Management and director fees 8</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
